--- a/docs/exemple_CAMWATER_Pointage_General.xlsx
+++ b/docs/exemple_CAMWATER_Pointage_General.xlsx
@@ -12,15 +12,17 @@
     <sheet name="Journal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MINSANTE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MINESEC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DGSN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Lignes écartées" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DGSN" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Résumé'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Résumé'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anomalies'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MINSANTE'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MINESEC'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DGSN'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Lignes écartées'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DGSN'!$A$1:$T$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +48,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +92,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -462,6 +471,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,35 +487,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>État</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Nb lignes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Consommation (m³)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Montant HT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Montant TTC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Lignes à vérifier</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lignes illisibles</t>
         </is>
@@ -522,11 +537,13 @@
           <t>mars-2026</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Reçue</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -537,10 +554,13 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -555,27 +575,32 @@
           <t>mars-2026</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reçue</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>70260</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>13526</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>83786</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -588,27 +613,32 @@
           <t>mars-2026</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Reçue</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>62120</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>11958</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>74078</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -617,30 +647,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>132380</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>25484</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>157864</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -651,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -708,32 +739,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DGSN</t>
+          <t>MINSANTE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>ÉCARTÉE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0012345678</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PL-9002</t>
+          <t>PL-8123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COMMISSARIAT CENTRAL N 1</t>
+          <t>SERVICE NON IDENTIFIE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Colonne obligatoire « Consommation » illisible et non reconstructible</t>
+          <t>Ligne nulle : aucun numéro de compte client — écartée du pointage</t>
         </is>
       </c>
     </row>
@@ -770,7 +801,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Colonne obligatoire « Montant HT » illisible et non reconstructible</t>
+          <t>Colonne obligatoire « Consommation » illisible et non reconstructible</t>
         </is>
       </c>
     </row>
@@ -807,7 +838,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Colonne obligatoire « TVA » illisible et non reconstructible</t>
+          <t>Colonne obligatoire « Montant HT » illisible et non reconstructible</t>
         </is>
       </c>
     </row>
@@ -843,6 +874,43 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Colonne obligatoire « TVA » illisible et non reconstructible</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>exemple-facture-mars-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DGSN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ILLISIBLE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0012345678</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PL-9002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMMISSARIAT CENTRAL N 1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Colonne obligatoire « Montant TTC » illisible et non reconstructible</t>
         </is>
@@ -860,18 +928,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -897,25 +968,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Compte client</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Période</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Lignes écrites</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Lignes à vérifier</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lignes illisibles</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Lignes écartées</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiance</t>
         </is>
@@ -924,7 +1010,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11 16:50:16</t>
+          <t>2026-08-11 19:20:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -942,24 +1028,37 @@
           <t>poste-demo</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0012345678</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mars-2026</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1649,73 +1748,300 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
+          <t>ILLISIBLE</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>MINISTERE DE LA SANTE PUBLIQUE</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>YAOUNDE</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>PL-8123</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>SERVICE NON IDENTIFIE</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>E112233</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>735</v>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>3820</v>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>MINSANTE</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>4555</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>ÉCARTÉE</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>exemple-facture-mars-2026.pdf</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>Ligne nulle : aucun numéro de compte client — écartée du pointage</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agence</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Période</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Compte client</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nom du client</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Code abonnement (PL)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Nom abonné</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>N° compteur</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Index nouvel</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Index ancien</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Consommation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Location compteur</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Montant HT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ministère_2026</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Montant TTC</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fichier source</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Anomalies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>DR CENTRE</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>0231</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>mars-2026</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
           <t>0012345678</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>MINISTERE DE LA SANTE PUBLIQUE</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>YAOUNDE</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>PL-9002</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>COMMISSARIAT CENTRAL N 1</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>D998877</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>DGSN</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>ILLISIBLE</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>exemple-facture-mars-2026.pdf</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>Colonne obligatoire « Consommation » illisible et non reconstructible | Colonne obligatoire « Montant HT » illisible et non reconstructible | Colonne obligatoire « TVA » illisible et non reconstructible | Colonne obligatoire « Montant TTC » illisible et non reconstructible</t>
         </is>
